--- a/KG/sample_data/class_level_data_main.xlsx
+++ b/KG/sample_data/class_level_data_main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Iris\practice\GenAI\code\Batch_KG\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F191C562-813F-459A-AE5A-B76371391951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5200A14-51AC-40F9-A9B0-1E9D4ED576BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobGroups" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="179">
   <si>
     <t>id</t>
   </si>
@@ -59,51 +59,18 @@
     <t>enabled</t>
   </si>
   <si>
-    <t>JG_EOD</t>
-  </si>
-  <si>
     <t>CRITICAL</t>
   </si>
   <si>
     <t>jobGroupId</t>
   </si>
   <si>
-    <t>NEW-BB-FUNDING-RATES-DOWNLOAD</t>
-  </si>
-  <si>
-    <t>AR-ML-LS2-TRIGGER</t>
-  </si>
-  <si>
-    <t>CODE-DESC</t>
-  </si>
-  <si>
-    <t>ONLINE-TO-HIST-SYNC-EXCEPTIONS</t>
-  </si>
-  <si>
-    <t>APMS-LL-AWS-S3-UPLOAD</t>
-  </si>
-  <si>
-    <t>LOANIQ-PAST-DUE-DATA</t>
-  </si>
-  <si>
-    <t>LS2H-DAILY-PREP</t>
-  </si>
-  <si>
-    <t>NEW-LOANIQ-COLLATERAL-MIG</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
     <t>checkInterval</t>
   </si>
   <si>
-    <t>s3://batch-data/input/file_1.csv</t>
-  </si>
-  <si>
-    <t>FILE</t>
-  </si>
-  <si>
     <t>resourceId</t>
   </si>
   <si>
@@ -137,81 +104,6 @@
     <t>forEntityId</t>
   </si>
   <si>
-    <t>SLA_0001</t>
-  </si>
-  <si>
-    <t>SLA_0002</t>
-  </si>
-  <si>
-    <t>SLA_0003</t>
-  </si>
-  <si>
-    <t>SLA_0004</t>
-  </si>
-  <si>
-    <t>SLA_0005</t>
-  </si>
-  <si>
-    <t>SLA_0006</t>
-  </si>
-  <si>
-    <t>SLA_0007</t>
-  </si>
-  <si>
-    <t>SLA_0008</t>
-  </si>
-  <si>
-    <t>SLA_0009</t>
-  </si>
-  <si>
-    <t>SLA_0010</t>
-  </si>
-  <si>
-    <t>SLA_0011</t>
-  </si>
-  <si>
-    <t>SLA_0012</t>
-  </si>
-  <si>
-    <t>SLA_NEW-BB-FUNDING-RATES-DOWNLOAD</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>Job</t>
-  </si>
-  <si>
-    <t>SLA_AR-ML-LS2-TRIGGER</t>
-  </si>
-  <si>
-    <t>SLA_CODE-DESC</t>
-  </si>
-  <si>
-    <t>SLA_ONLINE-TO-HIST-SYNC-EXCEPTIONS</t>
-  </si>
-  <si>
-    <t>SLA_APMS-LL-AWS-S3-UPLOAD</t>
-  </si>
-  <si>
-    <t>SLA_LOANIQ-PAST-DUE-DATA</t>
-  </si>
-  <si>
-    <t>SLA_LS2H-DAILY-PREP</t>
-  </si>
-  <si>
-    <t>SLA_NEW-LOANIQ-COLLATERAL-MIG</t>
-  </si>
-  <si>
-    <t>SLA_End of Day Processing</t>
-  </si>
-  <si>
-    <t>finish_by_time</t>
-  </si>
-  <si>
-    <t>JobGroup</t>
-  </si>
-  <si>
     <t>blockedDays</t>
   </si>
   <si>
@@ -407,261 +299,45 @@
     <t>Allowed</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>Position File Dependancy</t>
-  </si>
-  <si>
-    <t>Account File Dependancy</t>
-  </si>
-  <si>
-    <t>Commercial Exposure Extract</t>
-  </si>
-  <si>
-    <t>Wait for Position File Dependancy</t>
-  </si>
-  <si>
-    <t>Wait for Account File Dependancy</t>
-  </si>
-  <si>
-    <t>Wait for Commercial Exposure Extract</t>
-  </si>
-  <si>
-    <t>RES_001</t>
-  </si>
-  <si>
-    <t>RES_002</t>
-  </si>
-  <si>
-    <t>RES_003</t>
-  </si>
-  <si>
-    <t>Position File Resource</t>
-  </si>
-  <si>
-    <t>RES_004</t>
-  </si>
-  <si>
-    <t>RES_005</t>
-  </si>
-  <si>
-    <t>RES_006</t>
-  </si>
-  <si>
-    <t>RES_016</t>
-  </si>
-  <si>
     <t>dependencyType</t>
   </si>
   <si>
-    <t>INCOMING</t>
-  </si>
-  <si>
-    <t>OUTGOING</t>
-  </si>
-  <si>
-    <t>Account Balance Calculation</t>
-  </si>
-  <si>
-    <t>Generate Account Balance Calculation</t>
-  </si>
-  <si>
     <t>block</t>
   </si>
   <si>
     <t>SIMPLE</t>
   </si>
   <si>
-    <t>ScheduleInstanceContext</t>
-  </si>
-  <si>
     <t>durationMs</t>
   </si>
   <si>
-    <t>RELATIVE</t>
-  </si>
-  <si>
-    <t>ABSOLUTE</t>
-  </si>
-  <si>
-    <t>SLA_0013</t>
-  </si>
-  <si>
-    <t>duration_less_than</t>
-  </si>
-  <si>
-    <t>duration_relative</t>
-  </si>
-  <si>
     <t>relativeEntityId</t>
   </si>
   <si>
-    <t>SLA_Position File Resource</t>
-  </si>
-  <si>
-    <t>SLA_Account File Resource</t>
-  </si>
-  <si>
-    <t>SLA_Commercial Exposure Extract Resource</t>
-  </si>
-  <si>
-    <t>SLA_Account Balance Calculation Resource</t>
-  </si>
-  <si>
-    <t>available_by_time</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>Resource</t>
-  </si>
-  <si>
     <t>relativeEntityType</t>
   </si>
   <si>
     <t>tagType</t>
   </si>
   <si>
-    <t>Business</t>
-  </si>
-  <si>
-    <t>INPUT_FILE</t>
-  </si>
-  <si>
     <t>schemaName</t>
   </si>
   <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>CUSTOMER_POSITION_DATA</t>
-  </si>
-  <si>
-    <t>CUSTOMER_ACCOUNT_DATA</t>
-  </si>
-  <si>
-    <t>COMMERCIAL_EXPOSURE</t>
-  </si>
-  <si>
-    <t>ACCOUNT_BALANCE</t>
-  </si>
-  <si>
-    <t>LOAN_BALANCE</t>
-  </si>
-  <si>
     <t>tagId</t>
   </si>
   <si>
-    <t>TAG_CUSTOMER_POSITION_DATA</t>
-  </si>
-  <si>
-    <t>TAG_CUSTOMER_ACCOUNT_DATA</t>
-  </si>
-  <si>
-    <t>TAG_COMMERCIAL_EXPOSURE</t>
-  </si>
-  <si>
-    <t>TAG_ACCOUNT_BALANCE</t>
-  </si>
-  <si>
-    <t>TAG_LOAN_BALANCE</t>
-  </si>
-  <si>
-    <t>[TAG_CUSTOMER_POSITION_DATA]</t>
-  </si>
-  <si>
     <t>filePath</t>
   </si>
   <si>
-    <t>TABLE</t>
-  </si>
-  <si>
-    <t>TAG_INPUT_FILE</t>
-  </si>
-  <si>
     <t>Technical</t>
   </si>
   <si>
-    <t>Tag for input files</t>
-  </si>
-  <si>
-    <t>[TAG_CUSTOMER_DATA]</t>
-  </si>
-  <si>
-    <t>TAG_CUSTOMER_DATA</t>
-  </si>
-  <si>
-    <t>TAG_CUSTOMER_AGGREGATE_DATA</t>
-  </si>
-  <si>
-    <t>TAG_CUSTOMER_TRANSACTION_DATA</t>
-  </si>
-  <si>
-    <t>TAG_CUSTOMER_TMP_DATA</t>
-  </si>
-  <si>
-    <t>TAG_CUSTOMER_HIST_DATA</t>
-  </si>
-  <si>
-    <t>TAG_CUSTOMER_LOAN_DATA</t>
-  </si>
-  <si>
-    <t>TAG_CUSTOMER_LS_DATA</t>
-  </si>
-  <si>
-    <t>CUSTOMER_DATA</t>
-  </si>
-  <si>
-    <t>CUSTOMER_AGGREGATE_DATA</t>
-  </si>
-  <si>
-    <t>CUSTOMER_TRANSACTION_DATA</t>
-  </si>
-  <si>
-    <t>CUSTOMER_TMP_DATA</t>
-  </si>
-  <si>
-    <t>CUSTOMER_HIST_DATA</t>
-  </si>
-  <si>
-    <t>CUSTOMER_LOAN_DATA</t>
-  </si>
-  <si>
-    <t>CUSTOMER_LS_DATA</t>
-  </si>
-  <si>
-    <t>JG_EMP</t>
-  </si>
-  <si>
-    <t>SLA_Early Morning Processing</t>
-  </si>
-  <si>
-    <t>SLA_0014</t>
-  </si>
-  <si>
     <t>estimatedDurationMs</t>
   </si>
   <si>
     <t>realSLA</t>
   </si>
   <si>
-    <t>SLA_Mid Day Processing</t>
-  </si>
-  <si>
-    <t>JG_MID</t>
-  </si>
-  <si>
-    <t>Loan Amount Extract</t>
-  </si>
-  <si>
-    <t>TAG_LOAN_AMOUNT_EXTRACT</t>
-  </si>
-  <si>
-    <t>LOAN_AMOUNT_EXTRACT</t>
-  </si>
-  <si>
     <t>ctx_0012</t>
   </si>
   <si>
@@ -689,12 +365,6 @@
     <t>ctx_0020</t>
   </si>
   <si>
-    <t>SLA_0015</t>
-  </si>
-  <si>
-    <t>JG_TEST</t>
-  </si>
-  <si>
     <t>ctx_0022</t>
   </si>
   <si>
@@ -713,12 +383,6 @@
     <t>ctx_0028</t>
   </si>
   <si>
-    <t>SLA_0016</t>
-  </si>
-  <si>
-    <t>SLA_TEST Job Group</t>
-  </si>
-  <si>
     <t>jobId</t>
   </si>
   <si>
@@ -794,13 +458,7 @@
     <t>TAG_WEEKEND_END_DATE</t>
   </si>
   <si>
-    <t>JG_TEST2</t>
-  </si>
-  <si>
     <t>ctx_0029</t>
-  </si>
-  <si>
-    <t>SLA_TEST2 Job Group</t>
   </si>
   <si>
     <t>JG_0001</t>
@@ -999,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1010,14 +668,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1346,16 +1002,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>144</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1363,16 +1019,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
-        <v>259</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>264</v>
+        <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1380,16 +1036,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
       <c r="B4" t="s">
-        <v>260</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>265</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -1397,16 +1053,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>261</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>266</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1414,16 +1070,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>262</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
-        <v>267</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -1455,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -1466,16 +1122,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
         <v>65</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D2" t="s">
-        <v>101</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -1483,16 +1139,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -1500,16 +1156,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -1517,16 +1173,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1534,16 +1190,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -1551,16 +1207,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -1568,16 +1224,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -1599,210 +1255,210 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>113</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>268</v>
+        <v>154</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>269</v>
+        <v>155</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>270</v>
+        <v>156</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>271</v>
+        <v>157</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>273</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>274</v>
+        <v>160</v>
       </c>
       <c r="B8" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>275</v>
+        <v>161</v>
       </c>
       <c r="B9" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>276</v>
+        <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>278</v>
+        <v>164</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>282</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>283</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>284</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>286</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>287</v>
+        <v>173</v>
       </c>
       <c r="B21" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>288</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>289</v>
+        <v>175</v>
       </c>
       <c r="B23" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>290</v>
+        <v>176</v>
       </c>
       <c r="B24" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>291</v>
+        <v>177</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>292</v>
+        <v>178</v>
       </c>
       <c r="B26" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1834,69 +1490,29 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>60</v>
-      </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>175</v>
-      </c>
-    </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>181</v>
-      </c>
+      <c r="B3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B4"/>
@@ -1943,45 +1559,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>268</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="G2">
         <v>260000</v>
@@ -1992,19 +1608,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="G3">
         <v>370000</v>
@@ -2015,19 +1631,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>270</v>
+        <v>156</v>
       </c>
       <c r="C4" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G4">
         <v>420000</v>
@@ -2038,19 +1654,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>271</v>
+        <v>157</v>
       </c>
       <c r="C5" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G5">
         <v>400000</v>
@@ -2061,19 +1677,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>272</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G6">
         <v>670000</v>
@@ -2084,16 +1700,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>273</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>253</v>
+        <v>139</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G7">
         <v>360000</v>
@@ -2104,22 +1720,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>274</v>
+        <v>160</v>
       </c>
       <c r="C8" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G8">
         <v>380000</v>
@@ -2130,19 +1746,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>275</v>
+        <v>161</v>
       </c>
       <c r="C9" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G9">
         <v>280000</v>
@@ -2153,19 +1769,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>276</v>
+        <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>206</v>
+        <v>98</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G10">
         <v>420000</v>
@@ -2176,16 +1792,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>206</v>
+        <v>98</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="C11" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G11">
         <v>250000</v>
@@ -2196,22 +1812,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>278</v>
+        <v>164</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>208</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G12">
         <v>380000</v>
@@ -2222,19 +1838,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>208</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>279</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G13">
         <v>410000</v>
@@ -2245,19 +1861,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>209</v>
+        <v>101</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G14">
         <v>450000</v>
@@ -2268,19 +1884,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>281</v>
+        <v>167</v>
       </c>
       <c r="C15" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G15">
         <v>590000</v>
@@ -2291,16 +1907,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>168</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>141</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G16">
         <v>350000</v>
@@ -2311,22 +1927,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>212</v>
+        <v>104</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>283</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>213</v>
+        <v>105</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G17">
         <v>360000</v>
@@ -2337,16 +1953,16 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>213</v>
+        <v>105</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>284</v>
+        <v>170</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>142</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G18">
         <v>320000</v>
@@ -2357,22 +1973,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>214</v>
+        <v>106</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>285</v>
+        <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G19">
         <v>390000</v>
@@ -2383,19 +1999,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>217</v>
+        <v>107</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>286</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>218</v>
+        <v>108</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G20">
         <v>20000</v>
@@ -2406,19 +2022,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>218</v>
+        <v>108</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>287</v>
+        <v>173</v>
       </c>
       <c r="C21" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>219</v>
+        <v>109</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G21">
         <v>15000</v>
@@ -2429,19 +2045,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>219</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>288</v>
+        <v>174</v>
       </c>
       <c r="C22" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G22">
         <v>25000</v>
@@ -2452,19 +2068,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>289</v>
+        <v>175</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G23">
         <v>10000</v>
@@ -2475,19 +2091,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="B24" t="s">
-        <v>290</v>
+        <v>176</v>
       </c>
       <c r="C24" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G24">
         <v>5000</v>
@@ -2498,19 +2114,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>222</v>
+        <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>291</v>
+        <v>177</v>
       </c>
       <c r="C25" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G25">
         <v>10000</v>
@@ -2521,16 +2137,16 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>251</v>
+        <v>138</v>
       </c>
       <c r="B26" t="s">
-        <v>292</v>
+        <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>143</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="G26" s="3">
         <v>12000</v>
@@ -2570,161 +2186,38 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="F2" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>137</v>
-      </c>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2734,7 +2227,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="40.1796875" bestFit="1" customWidth="1"/>
@@ -2759,551 +2252,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>158</v>
+        <v>15</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>90</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G2">
-        <v>360000</v>
-      </c>
-      <c r="I2" t="s">
-        <v>145</v>
-      </c>
-      <c r="J2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3">
-        <v>300000</v>
-      </c>
-      <c r="I3" t="s">
-        <v>145</v>
-      </c>
-      <c r="J3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G4">
-        <v>420000</v>
-      </c>
-      <c r="I4" t="s">
-        <v>145</v>
-      </c>
-      <c r="J4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F5" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5">
-        <v>600000</v>
-      </c>
-      <c r="I5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6">
-        <v>300000</v>
-      </c>
-      <c r="I6" t="s">
-        <v>145</v>
-      </c>
-      <c r="J6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G7">
-        <v>540000</v>
-      </c>
-      <c r="I7" t="s">
-        <v>145</v>
-      </c>
-      <c r="J7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G8">
-        <v>240000</v>
-      </c>
-      <c r="I8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J8" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G9">
-        <v>360000</v>
-      </c>
-      <c r="I9" t="s">
-        <v>145</v>
-      </c>
-      <c r="J9" t="s">
-        <v>44</v>
-      </c>
-      <c r="K9" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10">
-        <v>3600000</v>
-      </c>
-      <c r="I10" t="s">
-        <v>145</v>
-      </c>
-      <c r="J10" t="s">
-        <v>44</v>
-      </c>
-      <c r="K10" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" t="s">
-        <v>146</v>
-      </c>
-      <c r="J11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K11" t="s">
-        <v>157</v>
-      </c>
-      <c r="L11" t="s">
-        <v>128</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" t="s">
-        <v>146</v>
-      </c>
-      <c r="J12" t="s">
-        <v>6</v>
-      </c>
-      <c r="K12" t="s">
-        <v>157</v>
-      </c>
-      <c r="L12" t="s">
-        <v>129</v>
-      </c>
-      <c r="M12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="H13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" t="s">
-        <v>146</v>
-      </c>
-      <c r="J13" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" t="s">
-        <v>157</v>
-      </c>
-      <c r="L13" t="s">
-        <v>130</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" t="s">
-        <v>146</v>
-      </c>
-      <c r="J14" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" t="s">
-        <v>157</v>
-      </c>
-      <c r="L14" t="s">
-        <v>132</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>198</v>
-      </c>
-      <c r="B15" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.29236111111111113</v>
-      </c>
-      <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" t="s">
-        <v>146</v>
-      </c>
-      <c r="J15" t="s">
-        <v>6</v>
-      </c>
-      <c r="K15" t="s">
-        <v>55</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>215</v>
-      </c>
-      <c r="B16" t="s">
-        <v>201</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G16">
-        <v>3200000</v>
-      </c>
-      <c r="I16" t="s">
-        <v>145</v>
-      </c>
-      <c r="J16" t="s">
-        <v>44</v>
-      </c>
-      <c r="K16" t="s">
-        <v>55</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="M16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>223</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G17">
-        <v>60000</v>
-      </c>
-      <c r="I17" t="s">
-        <v>145</v>
-      </c>
-      <c r="J17" t="s">
-        <v>44</v>
-      </c>
-      <c r="K17" t="s">
-        <v>55</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G18">
-        <v>60000</v>
-      </c>
-      <c r="I18" t="s">
-        <v>145</v>
-      </c>
-      <c r="J18" t="s">
-        <v>44</v>
-      </c>
-      <c r="K18" t="s">
-        <v>55</v>
-      </c>
-      <c r="L18" t="s">
-        <v>250</v>
-      </c>
-      <c r="M18" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3336,19 +2315,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>2</v>
@@ -3359,19 +2338,19 @@
     </row>
     <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -3379,25 +2358,25 @@
     </row>
     <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -3405,16 +2384,16 @@
     </row>
     <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -3422,16 +2401,16 @@
     </row>
     <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -3439,16 +2418,16 @@
     </row>
     <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -3456,19 +2435,19 @@
     </row>
     <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -3481,7 +2460,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2457C5B2-79A5-4ABF-A9FF-0D9D109676D8}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.7265625" bestFit="1" customWidth="1"/>
@@ -3499,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -3510,376 +2489,138 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="C5" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>179</v>
+        <v>95</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="C8" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>189</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B10" t="s">
-        <v>191</v>
-      </c>
-      <c r="C10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>185</v>
-      </c>
-      <c r="B11" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>186</v>
-      </c>
-      <c r="B12" t="s">
-        <v>193</v>
-      </c>
-      <c r="C12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>188</v>
-      </c>
-      <c r="B14" t="s">
-        <v>195</v>
-      </c>
-      <c r="C14" t="s">
-        <v>160</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>204</v>
-      </c>
-      <c r="B15" t="s">
-        <v>205</v>
-      </c>
-      <c r="C15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>242</v>
-      </c>
-      <c r="B16" t="s">
-        <v>234</v>
-      </c>
-      <c r="C16" t="s">
-        <v>179</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>243</v>
-      </c>
-      <c r="B17" t="s">
-        <v>235</v>
-      </c>
-      <c r="C17" t="s">
-        <v>179</v>
-      </c>
-      <c r="D17" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>244</v>
-      </c>
-      <c r="B18" t="s">
-        <v>236</v>
-      </c>
-      <c r="C18" t="s">
-        <v>179</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>245</v>
-      </c>
-      <c r="B19" t="s">
-        <v>237</v>
-      </c>
-      <c r="C19" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>246</v>
-      </c>
-      <c r="B20" t="s">
-        <v>238</v>
-      </c>
-      <c r="C20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>247</v>
-      </c>
-      <c r="B21" t="s">
-        <v>239</v>
-      </c>
-      <c r="C21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>248</v>
-      </c>
-      <c r="B22" t="s">
-        <v>240</v>
-      </c>
-      <c r="C22" t="s">
-        <v>179</v>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>249</v>
-      </c>
-      <c r="B23" t="s">
-        <v>241</v>
-      </c>
-      <c r="C23" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>233</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3889,7 +2630,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05669172-4566-411C-BAD9-C6B812325413}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
@@ -3908,196 +2649,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>120</v>
+        <v>84</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" t="s">
-        <v>202</v>
-      </c>
-      <c r="E7" t="s">
-        <v>121</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" t="s">
-        <v>216</v>
-      </c>
-      <c r="E8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>102</v>
-      </c>
-      <c r="B9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" t="s">
-        <v>202</v>
-      </c>
-      <c r="E9" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/KG/sample_data/class_level_data_main.xlsx
+++ b/KG/sample_data/class_level_data_main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Iris\practice\GenAI\code\Batch_KG\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5200A14-51AC-40F9-A9B0-1E9D4ED576BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53C31EE-2274-420A-815B-9CE4A81D2082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobGroups" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="179">
   <si>
     <t>id</t>
   </si>
@@ -976,14 +976,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -999,8 +999,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>139</v>
       </c>
@@ -1016,8 +1019,11 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>140</v>
       </c>
@@ -1033,8 +1039,11 @@
       <c r="E3" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>141</v>
       </c>
@@ -1050,8 +1059,11 @@
       <c r="E4" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>142</v>
       </c>
@@ -1067,8 +1079,11 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>143</v>
       </c>
